--- a/tmp/import-smoke/import-merge.xlsx
+++ b/tmp/import-smoke/import-merge.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,100 +439,105 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Importance</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Category OLD</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>FLAG</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Founding year</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Size adjusted</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>LinkedIn count</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Cantone</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Postal code</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Email organization</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Name personal contact</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Email personal contact (1)</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Email personal contact (2)</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Main Email personal contact</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Solution type</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Solution keyword 1</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Solution keyword 2</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Solution description</t>
         </is>
@@ -559,30 +564,31 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>alice@smoke-org.example</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>new@smoke-org.example</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
